--- a/data/trans_orig/P16A_n_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267798</t>
+          <t>267800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245816</t>
+          <t>246121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>257665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516504</t>
+          <t>516426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529161</t>
+          <t>529699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13085</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29296</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>26070</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>18073</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>37173</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20001</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12451</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29656</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>26070</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>17688</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>37021</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480217</t>
+          <t>479897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491048</t>
+          <t>490944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>483948</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>474653</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>490864</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>970954</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>959851</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>978951</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>483948</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>474293</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491498</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>970954</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>960003</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>979336</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,62 +1454,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5690</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313103</t>
+          <t>313467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648568</t>
+          <t>649478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351744</t>
+          <t>351481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357833</t>
+          <t>357826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356954</t>
+          <t>356776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368330</t>
+          <t>367800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712074</t>
+          <t>712116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724526</t>
+          <t>724618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199180</t>
+          <t>198396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198390</t>
+          <t>196710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206676</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400080</t>
+          <t>400276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409102</t>
+          <t>409160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265440</t>
+          <t>265217</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270062</t>
+          <t>269567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277243</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538424</t>
+          <t>537477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547127</t>
+          <t>547116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37101</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591612</t>
+          <t>592572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607937</t>
+          <t>607985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618866</t>
+          <t>616908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631429</t>
+          <t>630762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1216145</t>
+          <t>1216222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1235804</t>
+          <t>1235758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44642</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39818</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71210</t>
+          <t>67235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>710592</t>
+          <t>711738</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>730006</t>
+          <t>730028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738869</t>
+          <t>738491</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761127</t>
+          <t>761473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1456096</t>
+          <t>1460071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1487488</t>
+          <t>1489307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>71158</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>107516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113981</t>
+          <t>113739</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>160060</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3212015</t>
+          <t>3213619</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3239951</t>
+          <t>3239811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3270951</t>
+          <t>3271681</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3309818</t>
+          <t>3308039</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6494626</t>
+          <t>6495681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6541760</t>
+          <t>6542002</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279197</t>
+          <t>279049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292837</t>
+          <t>292770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271772</t>
+          <t>272938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283353</t>
+          <t>283385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556574</t>
+          <t>556660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574866</t>
+          <t>573325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>46879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473419</t>
+          <t>472398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494694</t>
+          <t>494000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475563</t>
+          <t>476886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499466</t>
+          <t>500542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959690</t>
+          <t>958568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989215</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317912</t>
+          <t>318355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329171</t>
+          <t>328500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338955</t>
+          <t>338962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651555</t>
+          <t>652141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662871</t>
+          <t>662889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>42329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>24338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>48442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362781</t>
+          <t>363211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372797</t>
+          <t>372823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345789</t>
+          <t>346622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367063</t>
+          <t>367393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715021</t>
+          <t>714491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738749</t>
+          <t>738595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30340</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54896</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195774</t>
+          <t>194529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208330</t>
+          <t>208135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175129</t>
+          <t>175069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196774</t>
+          <t>197837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377313</t>
+          <t>375038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401869</t>
+          <t>401885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266803</t>
+          <t>266947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266870</t>
+          <t>266327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277083</t>
+          <t>277058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538625</t>
+          <t>538402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>550002</t>
+          <t>550814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29277</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643582</t>
+          <t>643912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658381</t>
+          <t>657838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664576</t>
+          <t>663528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682021</t>
+          <t>681775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314728</t>
+          <t>1313588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337555</t>
+          <t>1336717</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>58093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>68843</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761394</t>
+          <t>761908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775767</t>
+          <t>775857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>766474</t>
+          <t>765760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>794120</t>
+          <t>793990</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1535453</t>
+          <t>1534108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1566878</t>
+          <t>1565460</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154178</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205263</t>
+          <t>203778</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>205742</t>
+          <t>210195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>271287</t>
+          <t>272328</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3346088</t>
+          <t>3345657</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3380918</t>
+          <t>3380279</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3353046</t>
+          <t>3354531</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3404131</t>
+          <t>3406019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6713801</t>
+          <t>6712760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6779346</t>
+          <t>6774893</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282903</t>
+          <t>282996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291353</t>
+          <t>291769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271982</t>
+          <t>271226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283686</t>
+          <t>284118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559046</t>
+          <t>558391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573768</t>
+          <t>574253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487946</t>
+          <t>487600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498824</t>
+          <t>498845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495241</t>
+          <t>495446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512610</t>
+          <t>512688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987013</t>
+          <t>988241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009388</t>
+          <t>1009755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313499</t>
+          <t>313015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322687</t>
+          <t>323151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333512</t>
+          <t>333723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638944</t>
+          <t>639263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651129</t>
+          <t>651039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39530</t>
+          <t>41381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,47 +8458,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>37768</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>26356</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>50949</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>4,99%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>37768</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26695</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>51216</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353964</t>
+          <t>354486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365362</t>
+          <t>365470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347753</t>
+          <t>345902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367964</t>
+          <t>367628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,47 +8571,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>706298</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>730891</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>95,01%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>706031</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>730552</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203324</t>
+          <t>203046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210416</t>
+          <t>210411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199792</t>
+          <t>199104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213334</t>
+          <t>213197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407032</t>
+          <t>408107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422332</t>
+          <t>422075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249872</t>
+          <t>249997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260478</t>
+          <t>260380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245820</t>
+          <t>246493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263071</t>
+          <t>263394</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501096</t>
+          <t>500777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521442</t>
+          <t>521735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54363</t>
+          <t>52514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629308</t>
+          <t>629275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647058</t>
+          <t>647070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>658546</t>
+          <t>657197</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677626</t>
+          <t>677536</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1293489</t>
+          <t>1295338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320738</t>
+          <t>1321400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56764</t>
+          <t>58685</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764791</t>
+          <t>764811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775906</t>
+          <t>776557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>769403</t>
+          <t>767482</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>796323</t>
+          <t>795198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1538592</t>
+          <t>1540530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1568835</t>
+          <t>1569780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>127474</t>
+          <t>130043</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>183207</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>181738</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3323413</t>
+          <t>3323018</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3351301</t>
+          <t>3351911</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3365891</t>
+          <t>3361335</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3417068</t>
+          <t>3414499</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6698957</t>
+          <t>6696860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6759731</t>
+          <t>6757154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299402</t>
+          <t>298870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308427</t>
+          <t>308215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>272636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282412</t>
+          <t>282442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575523</t>
+          <t>575524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588932</t>
+          <t>588524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30320</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49546</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>74409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487793</t>
+          <t>488170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506490</t>
+          <t>507540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465423</t>
+          <t>466143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484649</t>
+          <t>485203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960309</t>
+          <t>958950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987993</t>
+          <t>987051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57537</t>
+          <t>57995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58343</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84295</t>
+          <t>82391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284805</t>
+          <t>284444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300530</t>
+          <t>300159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291591</t>
+          <t>291133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310559</t>
+          <t>310928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580883</t>
+          <t>582787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>606835</t>
+          <t>608111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40217</t>
+          <t>39845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32704</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60043</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285210</t>
+          <t>284869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301127</t>
+          <t>301313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435501</t>
+          <t>435873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>458589</t>
+          <t>457712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728231</t>
+          <t>727281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>755570</t>
+          <t>754438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161526</t>
+          <t>160784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171344</t>
+          <t>171031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>220411</t>
+          <t>220068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>243545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386785</t>
+          <t>386865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409469</t>
+          <t>410027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35288</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41277</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50666</t>
+          <t>51504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71939</t>
+          <t>72443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234348</t>
+          <t>233870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249184</t>
+          <t>248453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215779</t>
+          <t>215688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230895</t>
+          <t>230458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454753</t>
+          <t>454249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476026</t>
+          <t>475188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93272</t>
+          <t>94562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108801</t>
+          <t>111206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594569</t>
+          <t>595124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611139</t>
+          <t>610548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>755993</t>
+          <t>754703</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>815898</t>
+          <t>819738</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1364743</t>
+          <t>1362338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1418543</t>
+          <t>1421532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60546</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92158</t>
+          <t>89217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63085</t>
+          <t>61706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130889</t>
+          <t>130954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>881572</t>
+          <t>881548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>916065</t>
+          <t>915006</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>625573</t>
+          <t>628514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>657185</t>
+          <t>657620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515563</t>
+          <t>1515498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1583367</t>
+          <t>1584746</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123430</t>
+          <t>122552</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>183887</t>
+          <t>181536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>264499</t>
+          <t>266250</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>364092</t>
+          <t>365936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>421523</t>
+          <t>415423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>536767</t>
+          <t>533785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3275930</t>
+          <t>3278281</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3336387</t>
+          <t>3337265</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3348188</t>
+          <t>3346344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3447781</t>
+          <t>3446030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6635330</t>
+          <t>6638312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6750574</t>
+          <t>6756674</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267800</t>
+          <t>267091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246121</t>
+          <t>245566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257665</t>
+          <t>257575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516426</t>
+          <t>517520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529699</t>
+          <t>529346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>36538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479897</t>
+          <t>480811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490944</t>
+          <t>490949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474653</t>
+          <t>473543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490864</t>
+          <t>491752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959851</t>
+          <t>960486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>978951</t>
+          <t>980529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313467</t>
+          <t>313613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649478</t>
+          <t>649499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351481</t>
+          <t>351499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>357837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356776</t>
+          <t>355282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367800</t>
+          <t>367457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712116</t>
+          <t>711340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724618</t>
+          <t>724364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198396</t>
+          <t>198601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196710</t>
+          <t>197412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206666</t>
+          <t>206452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400276</t>
+          <t>399595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409160</t>
+          <t>409107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265217</t>
+          <t>264598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269567</t>
+          <t>270043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537477</t>
+          <t>538134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547116</t>
+          <t>547206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592572</t>
+          <t>593059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607985</t>
+          <t>607940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>616908</t>
+          <t>617157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630762</t>
+          <t>631269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1216222</t>
+          <t>1215976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1235758</t>
+          <t>1235974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67235</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>711738</t>
+          <t>711648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>730028</t>
+          <t>729708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738491</t>
+          <t>739046</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761473</t>
+          <t>762609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1460071</t>
+          <t>1458622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1489307</t>
+          <t>1487480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>114323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3213619</t>
+          <t>3210501</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3239811</t>
+          <t>3239844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3271681</t>
+          <t>3270063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3308039</t>
+          <t>3308124</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6495681</t>
+          <t>6496676</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279049</t>
+          <t>278950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292770</t>
+          <t>291962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272938</t>
+          <t>272424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283385</t>
+          <t>283463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556660</t>
+          <t>556844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573325</t>
+          <t>574046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46879</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>73066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472398</t>
+          <t>473635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494000</t>
+          <t>494887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476886</t>
+          <t>476246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500542</t>
+          <t>499771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958568</t>
+          <t>956226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989128</t>
+          <t>990118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318355</t>
+          <t>318255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328500</t>
+          <t>328346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338962</t>
+          <t>338922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652141</t>
+          <t>652412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662889</t>
+          <t>662925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24338</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48442</t>
+          <t>49215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363211</t>
+          <t>362399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372823</t>
+          <t>372806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346622</t>
+          <t>346241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367393</t>
+          <t>366794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>714491</t>
+          <t>713718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738595</t>
+          <t>738463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>54651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194529</t>
+          <t>195920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208135</t>
+          <t>208342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175069</t>
+          <t>176795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197837</t>
+          <t>197360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375038</t>
+          <t>377558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401885</t>
+          <t>402379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266947</t>
+          <t>266865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266327</t>
+          <t>267105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277058</t>
+          <t>277864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538402</t>
+          <t>537692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>550814</t>
+          <t>549953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>42134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643912</t>
+          <t>644074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657838</t>
+          <t>657886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>663588</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681775</t>
+          <t>681984</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313588</t>
+          <t>1314507</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1336717</t>
+          <t>1336732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29863</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58093</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761908</t>
+          <t>762191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775857</t>
+          <t>776106</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>765760</t>
+          <t>767120</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>793990</t>
+          <t>793695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1534108</t>
+          <t>1537283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1565460</t>
+          <t>1566587</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>84898</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152290</t>
+          <t>151751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>205189</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>210195</t>
+          <t>209642</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>272328</t>
+          <t>270618</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3345657</t>
+          <t>3341881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3380279</t>
+          <t>3380041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3354531</t>
+          <t>3353120</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3406019</t>
+          <t>3406558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6712760</t>
+          <t>6714470</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6774893</t>
+          <t>6775446</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282996</t>
+          <t>282033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291769</t>
+          <t>291393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271226</t>
+          <t>271900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284118</t>
+          <t>284469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558391</t>
+          <t>559266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574253</t>
+          <t>573650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27638</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487600</t>
+          <t>488103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498845</t>
+          <t>499407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495446</t>
+          <t>495811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512688</t>
+          <t>512690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988241</t>
+          <t>988433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009755</t>
+          <t>1009680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313015</t>
+          <t>313017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323151</t>
+          <t>322158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333723</t>
+          <t>333738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639263</t>
+          <t>639682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651039</t>
+          <t>651195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354486</t>
+          <t>354548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365470</t>
+          <t>365500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345902</t>
+          <t>345140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367628</t>
+          <t>367646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706298</t>
+          <t>705664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730891</t>
+          <t>729496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203046</t>
+          <t>203254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210411</t>
+          <t>210417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199104</t>
+          <t>200202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213197</t>
+          <t>213369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>408107</t>
+          <t>408625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422075</t>
+          <t>422874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249997</t>
+          <t>250298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260380</t>
+          <t>260528</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246493</t>
+          <t>245347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263394</t>
+          <t>263223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500777</t>
+          <t>501839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521735</t>
+          <t>521462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629275</t>
+          <t>628953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647070</t>
+          <t>647098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>657197</t>
+          <t>657156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677536</t>
+          <t>677882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1295338</t>
+          <t>1294050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321400</t>
+          <t>1319272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58685</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>64002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764811</t>
+          <t>765296</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776557</t>
+          <t>776208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>767482</t>
+          <t>768473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>795198</t>
+          <t>796106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1540530</t>
+          <t>1540748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1569780</t>
+          <t>1570362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130043</t>
+          <t>129772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183207</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>241787</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3323018</t>
+          <t>3322325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3351911</t>
+          <t>3352453</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3361335</t>
+          <t>3366846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3414499</t>
+          <t>3414770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6696860</t>
+          <t>6697105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6757154</t>
+          <t>6756346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>304862</t>
+          <t>311962</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>298870</t>
+          <t>306339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308215</t>
+          <t>315799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278239</t>
+          <t>304640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272636</t>
+          <t>298664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282442</t>
+          <t>308876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>583100</t>
+          <t>616602</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575524</t>
+          <t>609331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588524</t>
+          <t>622700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48826</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>59511</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46308</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>499411</t>
+          <t>511136</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488170</t>
+          <t>500617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507540</t>
+          <t>518760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>476289</t>
+          <t>506494</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466143</t>
+          <t>495993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485203</t>
+          <t>515519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>975700</t>
+          <t>1017630</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958950</t>
+          <t>1001538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987051</t>
+          <t>1030016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69893</t>
+          <t>70226</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82391</t>
+          <t>83689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>293605</t>
+          <t>293942</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284444</t>
+          <t>284508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300159</t>
+          <t>300648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>301680</t>
+          <t>308206</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291133</t>
+          <t>296494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310928</t>
+          <t>316943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>595285</t>
+          <t>602149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582787</t>
+          <t>588686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608111</t>
+          <t>614404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29034</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>63363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>294778</t>
+          <t>353405</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284869</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301313</t>
+          <t>360303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>446684</t>
+          <t>391161</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435873</t>
+          <t>382505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457712</t>
+          <t>397563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>741461</t>
+          <t>744567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727281</t>
+          <t>731744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754438</t>
+          <t>755235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>23739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>34617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50656</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>167403</t>
+          <t>193859</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160784</t>
+          <t>188416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171031</t>
+          <t>198046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>229759</t>
+          <t>198923</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>220068</t>
+          <t>192343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243545</t>
+          <t>205179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>397162</t>
+          <t>392782</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386865</t>
+          <t>383601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410027</t>
+          <t>399965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>61621</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51504</t>
+          <t>51578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72443</t>
+          <t>72157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>242201</t>
+          <t>243642</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233870</t>
+          <t>235299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248453</t>
+          <t>250305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>223703</t>
+          <t>229195</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215688</t>
+          <t>220434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>230458</t>
+          <t>235781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465904</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454249</t>
+          <t>462300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475188</t>
+          <t>482879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68149</t>
+          <t>83423</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94562</t>
+          <t>99547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88699</t>
+          <t>108038</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52012</t>
+          <t>92674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111206</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>603729</t>
+          <t>695072</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595124</t>
+          <t>683920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610548</t>
+          <t>703701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>781116</t>
+          <t>688634</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>754703</t>
+          <t>672510</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>819738</t>
+          <t>701457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1384845</t>
+          <t>1383706</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1362338</t>
+          <t>1365245</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1421532</t>
+          <t>1399070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>46403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>78244</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89217</t>
+          <t>93353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>113988</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>97906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130954</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>897290</t>
+          <t>762328</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>881548</t>
+          <t>751669</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>915006</t>
+          <t>771275</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>645007</t>
+          <t>753087</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>628514</t>
+          <t>737978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>657620</t>
+          <t>766248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1542298</t>
+          <t>1515415</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515498</t>
+          <t>1496225</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1584746</t>
+          <t>1531497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>122552</t>
+          <t>146648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>181536</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>331277</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>365936</t>
+          <t>390470</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>415423</t>
+          <t>488369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>533785</t>
+          <t>561122</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3303280</t>
+          <t>3365347</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3278281</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3337265</t>
+          <t>3386114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3382475</t>
+          <t>3380340</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3346344</t>
+          <t>3346484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3446030</t>
+          <t>3405677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6685755</t>
+          <t>6745688</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6638312</t>
+          <t>6708594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6756674</t>
+          <t>6781347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
